--- a/fires_rules/firerules/tables.xlsx
+++ b/fires_rules/firerules/tables.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\lyx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\firerules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E604052F-6E96-48E2-B665-96739E38176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB7707F-9766-44CD-82A9-BE4AAF6B1C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5170" yWindow="2110" windowWidth="30530" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="720" windowWidth="10620" windowHeight="12020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Φύλλο1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="30">
   <si>
     <t>MLP (BFGS)</t>
   </si>
@@ -101,6 +112,21 @@
   <si>
     <t>Recall</t>
   </si>
+  <si>
+    <t>DATASET</t>
+  </si>
+  <si>
+    <t>MLP(BFGS)</t>
+  </si>
+  <si>
+    <t>FC2(MLP)</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>Eastern Macedonia &amp; Thrace</t>
+  </si>
 </sst>
 </file>
 
@@ -142,11 +168,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
@@ -717,6 +745,1004 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="el-GR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-7D31-4B52-84AD-283CA0A06F09}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7D31-4B52-84AD-283CA0A06F09}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7D31-4B52-84AD-283CA0A06F09}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-7D31-4B52-84AD-283CA0A06F09}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-7D31-4B52-84AD-283CA0A06F09}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Φύλλο1!$B$86:$G$86</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>MLP(BFGS)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RBF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RF</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FC2(RF)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FC2(MLP)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GENCLASS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Φύλλο1!$B$90:$G$90</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.1419</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.14030000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.13420000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.12920000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-7D31-4B52-84AD-283CA0A06F09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="80"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1315182479"/>
+        <c:axId val="1334134351"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1315182479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1334134351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1334134351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Classification</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> error [%]</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="el-GR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1315182479"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="el-GR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Φύλλο1!$A$54</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Precision</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Φύλλο1!$B$50:$G$50</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>MLP (BFGS)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RBF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RF</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FC2(RF)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FC2 (MLP)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GENCLASS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Φύλλο1!$B$54:$G$54</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>87.160000000000011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>83.676666666666662</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>87.529999999999987</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87.036666666666676</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>86.84666666666665</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87.523333333333326</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-74D2-47FD-BD79-00290377EE77}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Φύλλο1!$A$75</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Recall</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Φύλλο1!$B$50:$G$50</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>MLP (BFGS)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RBF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RF</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FC2(RF)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FC2 (MLP)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GENCLASS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Φύλλο1!$B$75:$G$75</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>86.526666666666657</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>83.743333333333325</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.910000000000011</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87.09333333333332</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>87.206666666666663</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-74D2-47FD-BD79-00290377EE77}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="l"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="433796031"/>
+        <c:axId val="342628815"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="433796031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="342628815"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="342628815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Average Rate</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> [%]</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="el-GR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="433796031"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -5309,6 +6335,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -5779,6 +6885,1025 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -10498,6 +12623,80 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Γράφημα 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EB8C29D-78BC-4183-85B8-06318DF2D28D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Γράφημα 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27ED020F-0A0D-1415-D5D2-B824A3E7F2D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10764,12 +12963,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G74"/>
+  <dimension ref="A2:G90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="11.81640625" customWidth="1"/>
+    <col min="3" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -11606,11 +13807,6 @@
         <v>15.11</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>0</v>
@@ -11700,9 +13896,33 @@
         <v>85.07</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
-        <v>24</v>
+    <row r="54" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" s="3">
+        <f>AVERAGE(B51:B53)</f>
+        <v>87.160000000000011</v>
+      </c>
+      <c r="C54" s="3">
+        <f t="shared" ref="C54:G54" si="0">AVERAGE(C51:C53)</f>
+        <v>83.676666666666662</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" si="0"/>
+        <v>87.529999999999987</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" si="0"/>
+        <v>87.036666666666676</v>
+      </c>
+      <c r="F54" s="3">
+        <f t="shared" si="0"/>
+        <v>86.84666666666665</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" si="0"/>
+        <v>87.523333333333326</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
@@ -11792,6 +14012,150 @@
       </c>
       <c r="G74">
         <v>85.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="3">
+        <f>AVERAGE(B72:B74)</f>
+        <v>86.526666666666657</v>
+      </c>
+      <c r="C75" s="3">
+        <f t="shared" ref="C75:G75" si="1">AVERAGE(C72:C74)</f>
+        <v>83.743333333333325</v>
+      </c>
+      <c r="D75" s="3">
+        <f t="shared" si="1"/>
+        <v>86.910000000000011</v>
+      </c>
+      <c r="E75" s="3">
+        <f t="shared" si="1"/>
+        <v>87.09333333333332</v>
+      </c>
+      <c r="F75" s="3">
+        <f t="shared" si="1"/>
+        <v>87.206666666666663</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="1"/>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" t="s">
+        <v>27</v>
+      </c>
+      <c r="G86" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87">
+        <v>13.67</v>
+      </c>
+      <c r="C87">
+        <v>14.42</v>
+      </c>
+      <c r="D87">
+        <v>13.93</v>
+      </c>
+      <c r="E87">
+        <v>13.01</v>
+      </c>
+      <c r="F87">
+        <v>12.82</v>
+      </c>
+      <c r="G87">
+        <v>12.43</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>29</v>
+      </c>
+      <c r="B88">
+        <v>12.51</v>
+      </c>
+      <c r="C88">
+        <v>15.34</v>
+      </c>
+      <c r="D88">
+        <v>12.21</v>
+      </c>
+      <c r="E88">
+        <v>11.93</v>
+      </c>
+      <c r="F88">
+        <v>11.87</v>
+      </c>
+      <c r="G88">
+        <v>11.47</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89">
+        <v>16.39</v>
+      </c>
+      <c r="C89">
+        <v>17.82</v>
+      </c>
+      <c r="D89">
+        <v>15.96</v>
+      </c>
+      <c r="E89">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="F89">
+        <v>15.56</v>
+      </c>
+      <c r="G89">
+        <v>14.86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" s="2">
+        <v>0.1419</v>
+      </c>
+      <c r="C90" s="2">
+        <v>0.15859999999999999</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.14030000000000001</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.12920000000000001</v>
       </c>
     </row>
   </sheetData>
